--- a/Sales_Performance_Dashboard.xlsx
+++ b/Sales_Performance_Dashboard.xlsx
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="486" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="492" uniqueCount="187">
   <si>
     <t>Order ID</t>
   </si>
@@ -1314,6 +1314,27 @@
         <c:marker>
           <c:symbol val="none"/>
         </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:layout/>
+          <c:spPr/>
+          <c:txPr>
+            <a:bodyPr/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr/>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbl>
       </c:pivotFmt>
     </c:pivotFmts>
     <c:plotArea>
@@ -1342,6 +1363,26 @@
             </a:solidFill>
           </c:spPr>
           <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr/>
+            <c:txPr>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+          </c:dLbls>
           <c:cat>
             <c:strRef>
               <c:f>'PVT. TABLE'!$A$45:$A$51</c:f>
@@ -1405,11 +1446,11 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="208695680"/>
-        <c:axId val="208697216"/>
+        <c:axId val="192377216"/>
+        <c:axId val="192378752"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="208695680"/>
+        <c:axId val="192377216"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1431,7 +1472,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="208697216"/>
+        <c:crossAx val="192378752"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1439,7 +1480,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="208697216"/>
+        <c:axId val="192378752"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1449,7 +1490,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="208695680"/>
+        <c:crossAx val="192377216"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1620,6 +1661,27 @@
         <c:marker>
           <c:symbol val="none"/>
         </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:layout/>
+          <c:spPr/>
+          <c:txPr>
+            <a:bodyPr/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr/>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbl>
       </c:pivotFmt>
     </c:pivotFmts>
     <c:plotArea>
@@ -1658,6 +1720,26 @@
             </a:solidFill>
           </c:spPr>
           <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr/>
+            <c:txPr>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+          </c:dLbls>
           <c:cat>
             <c:strRef>
               <c:f>'PVT. TABLE'!$H$45:$H$49</c:f>
@@ -1709,11 +1791,11 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="208723968"/>
-        <c:axId val="208725504"/>
+        <c:axId val="192405504"/>
+        <c:axId val="192407040"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="208723968"/>
+        <c:axId val="192405504"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1722,7 +1804,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="208725504"/>
+        <c:crossAx val="192407040"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1730,7 +1812,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="208725504"/>
+        <c:axId val="192407040"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1740,7 +1822,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="208723968"/>
+        <c:crossAx val="192405504"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2005,11 +2087,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="203258112"/>
-        <c:axId val="203264000"/>
+        <c:axId val="192116992"/>
+        <c:axId val="192122880"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="203258112"/>
+        <c:axId val="192116992"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2018,7 +2100,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="203264000"/>
+        <c:crossAx val="192122880"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2026,7 +2108,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="203264000"/>
+        <c:axId val="192122880"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2036,7 +2118,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="203258112"/>
+        <c:crossAx val="192116992"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2284,11 +2366,11 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="208763520"/>
-        <c:axId val="208765312"/>
+        <c:axId val="192443520"/>
+        <c:axId val="192445056"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="208763520"/>
+        <c:axId val="192443520"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2297,7 +2379,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="208765312"/>
+        <c:crossAx val="192445056"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2305,7 +2387,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="208765312"/>
+        <c:axId val="192445056"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2315,7 +2397,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="208763520"/>
+        <c:crossAx val="192443520"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2517,16 +2599,25 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'PVT. TABLE'!$H$13:$H$16</c:f>
+              <c:f>'PVT. TABLE'!$H$13:$H$19</c:f>
               <c:strCache>
-                <c:ptCount val="3"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
                   <c:v>Keyboard</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>Monitor</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>Mouse</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
+                  <c:v>Printer</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Scanner</c:v>
+                </c:pt>
+                <c:pt idx="5">
                   <c:v>Speaker</c:v>
                 </c:pt>
               </c:strCache>
@@ -2534,17 +2625,26 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'PVT. TABLE'!$I$13:$I$16</c:f>
+              <c:f>'PVT. TABLE'!$I$13:$I$19</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
                   <c:v>287</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>186</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>452</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
+                  <c:v>159</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>274</c:v>
+                </c:pt>
+                <c:pt idx="5">
                   <c:v>276</c:v>
                 </c:pt>
               </c:numCache>
@@ -2560,11 +2660,11 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="202783360"/>
-        <c:axId val="202793344"/>
+        <c:axId val="191641856"/>
+        <c:axId val="191660032"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="202783360"/>
+        <c:axId val="191641856"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2573,7 +2673,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="202793344"/>
+        <c:crossAx val="191660032"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2581,7 +2681,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="202793344"/>
+        <c:axId val="191660032"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2591,7 +2691,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="202783360"/>
+        <c:crossAx val="191641856"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2808,35 +2908,53 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'PVT. TABLE'!$O$13:$O$16</c:f>
+              <c:f>'PVT. TABLE'!$O$13:$O$19</c:f>
               <c:strCache>
-                <c:ptCount val="3"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
+                  <c:v>Keyboard</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>Monitor</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="2">
+                  <c:v>Mouse</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>Printer</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="4">
                   <c:v>Scanner</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Speaker</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'PVT. TABLE'!$P$13:$P$16</c:f>
+              <c:f>'PVT. TABLE'!$P$13:$P$19</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
+                  <c:v>287</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>186</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="2">
+                  <c:v>452</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>159</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="4">
                   <c:v>274</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>276</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2851,11 +2969,11 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="202828416"/>
-        <c:axId val="202834304"/>
+        <c:axId val="191687296"/>
+        <c:axId val="191693184"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="202828416"/>
+        <c:axId val="191687296"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2864,7 +2982,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="202834304"/>
+        <c:crossAx val="191693184"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2872,7 +2990,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="202834304"/>
+        <c:axId val="191693184"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2882,7 +3000,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="202828416"/>
+        <c:crossAx val="191687296"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3235,11 +3353,11 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="212936576"/>
-        <c:axId val="212938112"/>
+        <c:axId val="192488960"/>
+        <c:axId val="192490496"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="212936576"/>
+        <c:axId val="192488960"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3248,7 +3366,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="212938112"/>
+        <c:crossAx val="192490496"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3256,7 +3374,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="212938112"/>
+        <c:axId val="192490496"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3276,7 +3394,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="212936576"/>
+        <c:crossAx val="192488960"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3780,11 +3898,11 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="213326848"/>
-        <c:axId val="213336832"/>
+        <c:axId val="192879616"/>
+        <c:axId val="192889600"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="213326848"/>
+        <c:axId val="192879616"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3793,7 +3911,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="213336832"/>
+        <c:crossAx val="192889600"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3801,7 +3919,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="213336832"/>
+        <c:axId val="192889600"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3811,7 +3929,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="213326848"/>
+        <c:crossAx val="192879616"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4313,11 +4431,11 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="213401600"/>
-        <c:axId val="213403136"/>
+        <c:axId val="192950272"/>
+        <c:axId val="192951808"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="213401600"/>
+        <c:axId val="192950272"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4326,7 +4444,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="213403136"/>
+        <c:crossAx val="192951808"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4334,7 +4452,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="213403136"/>
+        <c:axId val="192951808"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4344,7 +4462,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="213401600"/>
+        <c:crossAx val="192950272"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -10545,8 +10663,8 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable11" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="4" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="4" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="26">
-  <location ref="W11:W12" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable5" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="4" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="4" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="26">
+  <location ref="A44:B51" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="9">
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
@@ -10576,7 +10694,7 @@
         <item t="default"/>
       </items>
     </pivotField>
-    <pivotField showAll="0">
+    <pivotField axis="axisRow" showAll="0">
       <items count="7">
         <item x="5"/>
         <item x="0"/>
@@ -10588,19 +10706,53 @@
       </items>
     </pivotField>
     <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
     <pivotField showAll="0"/>
-    <pivotField showAll="0" defaultSubtotal="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0" defaultSubtotal="0"/>
   </pivotFields>
-  <rowItems count="1">
-    <i/>
+  <rowFields count="1">
+    <field x="4"/>
+  </rowFields>
+  <rowItems count="7">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
   </rowItems>
   <colItems count="1">
     <i/>
   </colItems>
   <dataFields count="1">
-    <dataField name="Sum of Qty" fld="6" baseField="0" baseItem="0"/>
+    <dataField name="Sum of Total Sales" fld="8" baseField="0" baseItem="0"/>
   </dataFields>
+  <chartFormats count="1">
+    <chartFormat chart="19" format="3" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
@@ -10729,118 +10881,6 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable11.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="4" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="4" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="27">
-  <location ref="H29:I33" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="9">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="13">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="3"/>
-        <item x="10"/>
-        <item x="6"/>
-        <item x="8"/>
-        <item x="5"/>
-        <item x="4"/>
-        <item x="7"/>
-        <item x="9"/>
-        <item x="2"/>
-        <item x="11"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="5">
-        <item x="1"/>
-        <item x="2"/>
-        <item x="0"/>
-        <item x="3"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="7">
-        <item x="5"/>
-        <item x="0"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisRow" showAll="0" measureFilter="1">
-      <items count="9">
-        <item x="6"/>
-        <item x="2"/>
-        <item x="0"/>
-        <item x="7"/>
-        <item x="5"/>
-        <item x="4"/>
-        <item x="1"/>
-        <item x="3"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0" defaultSubtotal="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="5"/>
-  </rowFields>
-  <rowItems count="4">
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Sum of Total Sales" fld="8" baseField="0" baseItem="0"/>
-  </dataFields>
-  <chartFormats count="1">
-    <chartFormat chart="24" format="9" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <filters count="1">
-    <filter fld="5" type="count" evalOrder="-1" id="3" iMeasureFld="0">
-      <autoFilter ref="A1">
-        <filterColumn colId="0">
-          <top10 val="3" filterVal="3"/>
-        </filterColumn>
-      </autoFilter>
-    </filter>
-  </filters>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="4" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="4" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="24">
   <location ref="A12:B19" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="9">
@@ -10994,6 +11034,118 @@
 </pivotTableDefinition>
 </file>
 
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable4" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="4" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="4" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="27">
+  <location ref="O29:P33" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="9">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="13">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="3"/>
+        <item x="10"/>
+        <item x="6"/>
+        <item x="8"/>
+        <item x="5"/>
+        <item x="4"/>
+        <item x="7"/>
+        <item x="9"/>
+        <item x="2"/>
+        <item x="11"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="5">
+        <item x="1"/>
+        <item x="2"/>
+        <item x="0"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="7">
+        <item x="5"/>
+        <item x="0"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0" measureFilter="1">
+      <items count="9">
+        <item x="6"/>
+        <item x="2"/>
+        <item x="0"/>
+        <item x="7"/>
+        <item x="5"/>
+        <item x="4"/>
+        <item x="1"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0" defaultSubtotal="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="5"/>
+  </rowFields>
+  <rowItems count="4">
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Total Sales" fld="8" baseField="0" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="1">
+    <chartFormat chart="24" format="8" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <filters count="1">
+    <filter fld="5" type="count" evalOrder="-1" id="4" iMeasureFld="0">
+      <autoFilter ref="A1">
+        <filterColumn colId="0">
+          <top10 top="0" val="3" filterVal="3"/>
+        </filterColumn>
+      </autoFilter>
+    </filter>
+  </filters>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="4" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="4" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="26">
   <location ref="A26:B35" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
@@ -11113,74 +11265,8 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable8" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="4" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="4" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="26">
-  <location ref="W6:W7" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
-  <pivotFields count="9">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="13">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="3"/>
-        <item x="10"/>
-        <item x="6"/>
-        <item x="8"/>
-        <item x="5"/>
-        <item x="4"/>
-        <item x="7"/>
-        <item x="9"/>
-        <item x="2"/>
-        <item x="11"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="5">
-        <item x="1"/>
-        <item x="2"/>
-        <item x="0"/>
-        <item x="3"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="7">
-        <item x="5"/>
-        <item x="0"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0" defaultSubtotal="0"/>
-  </pivotFields>
-  <rowItems count="1">
-    <i/>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Sum of Total Sales" fld="8" baseField="0" baseItem="0"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable4" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="4" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="4" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="27">
-  <location ref="O29:P33" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="4" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="4" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="27">
+  <location ref="H29:I33" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="9">
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
@@ -11243,13 +11329,13 @@
   </rowFields>
   <rowItems count="4">
     <i>
-      <x v="1"/>
+      <x v="5"/>
     </i>
     <i>
-      <x v="3"/>
+      <x v="6"/>
     </i>
     <i>
-      <x v="4"/>
+      <x v="7"/>
     </i>
     <i t="grand">
       <x/>
@@ -11262,7 +11348,7 @@
     <dataField name="Sum of Total Sales" fld="8" baseField="0" baseItem="0"/>
   </dataFields>
   <chartFormats count="1">
-    <chartFormat chart="24" format="8" series="1">
+    <chartFormat chart="24" format="9" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
@@ -11274,14 +11360,186 @@
   </chartFormats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <filters count="1">
-    <filter fld="5" type="count" evalOrder="-1" id="4" iMeasureFld="0">
+    <filter fld="5" type="count" evalOrder="-1" id="3" iMeasureFld="0">
       <autoFilter ref="A1">
         <filterColumn colId="0">
-          <top10 top="0" val="3" filterVal="3"/>
+          <top10 val="3" filterVal="3"/>
         </filterColumn>
       </autoFilter>
     </filter>
   </filters>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable9" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="4" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="4" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="32">
+  <location ref="O12:P19" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="9">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="13">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="3"/>
+        <item x="10"/>
+        <item x="6"/>
+        <item x="8"/>
+        <item x="5"/>
+        <item x="4"/>
+        <item x="7"/>
+        <item x="9"/>
+        <item x="2"/>
+        <item x="11"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="5">
+        <item x="1"/>
+        <item x="2"/>
+        <item x="0"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="7">
+        <item x="5"/>
+        <item x="0"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0" defaultSubtotal="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="4"/>
+  </rowFields>
+  <rowItems count="7">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Qty" fld="6" baseField="0" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="9">
+    <chartFormat chart="0" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="1" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="2" format="1" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="3" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="6" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="9" format="1" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="21" format="8" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="24" format="1" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="31" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
       <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
@@ -11385,8 +11643,8 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable5" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="4" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="4" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="26">
-  <location ref="A44:B51" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable10" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="4" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="4" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="31">
+  <location ref="H12:I19" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="9">
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
@@ -11428,9 +11686,9 @@
       </items>
     </pivotField>
     <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
     <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0" defaultSubtotal="0"/>
+    <pivotField showAll="0" defaultSubtotal="0"/>
   </pivotFields>
   <rowFields count="1">
     <field x="4"/>
@@ -11450,269 +11708,6 @@
     </i>
     <i>
       <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Sum of Total Sales" fld="8" baseField="0" baseItem="0"/>
-  </dataFields>
-  <chartFormats count="1">
-    <chartFormat chart="19" format="3" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable8.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable9" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="4" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="4" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="32">
-  <location ref="O12:P16" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="9">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="13">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="3"/>
-        <item x="10"/>
-        <item x="6"/>
-        <item x="8"/>
-        <item x="5"/>
-        <item x="4"/>
-        <item x="7"/>
-        <item x="9"/>
-        <item x="2"/>
-        <item x="11"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="5">
-        <item x="1"/>
-        <item x="2"/>
-        <item x="0"/>
-        <item x="3"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisRow" showAll="0" measureFilter="1">
-      <items count="7">
-        <item x="5"/>
-        <item x="0"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0" defaultSubtotal="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="4"/>
-  </rowFields>
-  <rowItems count="4">
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Sum of Qty" fld="6" baseField="0" baseItem="0"/>
-  </dataFields>
-  <chartFormats count="9">
-    <chartFormat chart="0" format="2" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="1" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="2" format="1" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="3" format="2" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="6" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="9" format="1" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="21" format="8" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="24" format="1" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="31" format="2" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <filters count="1">
-    <filter fld="4" type="count" evalOrder="-1" id="3" iMeasureFld="0">
-      <autoFilter ref="A1">
-        <filterColumn colId="0">
-          <top10 top="0" val="3" filterVal="3"/>
-        </filterColumn>
-      </autoFilter>
-    </filter>
-  </filters>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable9.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable10" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="4" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="4" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="31">
-  <location ref="H12:I16" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="9">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="13">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="3"/>
-        <item x="10"/>
-        <item x="6"/>
-        <item x="8"/>
-        <item x="5"/>
-        <item x="4"/>
-        <item x="7"/>
-        <item x="9"/>
-        <item x="2"/>
-        <item x="11"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="5">
-        <item x="1"/>
-        <item x="2"/>
-        <item x="0"/>
-        <item x="3"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisRow" showAll="0" measureFilter="1">
-      <items count="7">
-        <item x="5"/>
-        <item x="0"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0" defaultSubtotal="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="4"/>
-  </rowFields>
-  <rowItems count="4">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="2"/>
     </i>
     <i>
       <x v="5"/>
@@ -11838,15 +11833,138 @@
     </chartFormat>
   </chartFormats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <filters count="1">
-    <filter fld="4" type="count" evalOrder="-1" id="4" iMeasureFld="0">
-      <autoFilter ref="A1">
-        <filterColumn colId="0">
-          <top10 val="3" filterVal="3"/>
-        </filterColumn>
-      </autoFilter>
-    </filter>
-  </filters>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable8.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable8" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="4" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="4" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="26">
+  <location ref="W6:W7" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
+  <pivotFields count="9">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="13">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="3"/>
+        <item x="10"/>
+        <item x="6"/>
+        <item x="8"/>
+        <item x="5"/>
+        <item x="4"/>
+        <item x="7"/>
+        <item x="9"/>
+        <item x="2"/>
+        <item x="11"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="5">
+        <item x="1"/>
+        <item x="2"/>
+        <item x="0"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="7">
+        <item x="5"/>
+        <item x="0"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0" defaultSubtotal="0"/>
+  </pivotFields>
+  <rowItems count="1">
+    <i/>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Total Sales" fld="8" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable9.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable11" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="4" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="4" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="26">
+  <location ref="W11:W12" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
+  <pivotFields count="9">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="13">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="3"/>
+        <item x="10"/>
+        <item x="6"/>
+        <item x="8"/>
+        <item x="5"/>
+        <item x="4"/>
+        <item x="7"/>
+        <item x="9"/>
+        <item x="2"/>
+        <item x="11"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="5">
+        <item x="1"/>
+        <item x="2"/>
+        <item x="0"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="7">
+        <item x="5"/>
+        <item x="0"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0" defaultSubtotal="0"/>
+  </pivotFields>
+  <rowItems count="1">
+    <i/>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Qty" fld="6" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
       <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
@@ -14916,7 +15034,7 @@
     <col min="6" max="6" width="10.7109375" customWidth="1"/>
     <col min="7" max="7" width="6.85546875" customWidth="1"/>
     <col min="8" max="8" width="13.140625" customWidth="1"/>
-    <col min="9" max="9" width="10.7109375" customWidth="1"/>
+    <col min="9" max="9" width="17.28515625" customWidth="1"/>
     <col min="10" max="10" width="19.5703125" customWidth="1"/>
     <col min="11" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="6.42578125" customWidth="1"/>
@@ -15002,10 +15120,10 @@
       </c>
       <c r="J13" s="3"/>
       <c r="O13" s="2" t="s">
-        <v>11</v>
+        <v>57</v>
       </c>
       <c r="P13" s="3">
-        <v>186</v>
+        <v>287</v>
       </c>
       <c r="Q13" s="3"/>
     </row>
@@ -15022,17 +15140,17 @@
       <c r="F14" s="3"/>
       <c r="G14" s="3"/>
       <c r="H14" s="2" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="I14" s="3">
-        <v>452</v>
+        <v>186</v>
       </c>
       <c r="J14" s="3"/>
       <c r="O14" s="2" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="P14" s="3">
-        <v>159</v>
+        <v>186</v>
       </c>
       <c r="Q14" s="3"/>
     </row>
@@ -15047,17 +15165,17 @@
       <c r="D15" s="3"/>
       <c r="E15" s="3"/>
       <c r="H15" s="2" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="I15" s="3">
-        <v>276</v>
+        <v>452</v>
       </c>
       <c r="J15" s="3"/>
       <c r="O15" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="P15" s="3">
-        <v>274</v>
+        <v>452</v>
       </c>
       <c r="Q15" s="3"/>
     </row>
@@ -15072,17 +15190,17 @@
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="H16" s="2" t="s">
-        <v>171</v>
+        <v>38</v>
       </c>
       <c r="I16" s="3">
-        <v>1015</v>
+        <v>159</v>
       </c>
       <c r="J16" s="3"/>
       <c r="O16" s="2" t="s">
-        <v>171</v>
+        <v>38</v>
       </c>
       <c r="P16" s="3">
-        <v>619</v>
+        <v>159</v>
       </c>
       <c r="Q16" s="3"/>
     </row>
@@ -15096,6 +15214,18 @@
       <c r="C17" s="3"/>
       <c r="D17" s="3"/>
       <c r="E17" s="3"/>
+      <c r="H17" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I17" s="3">
+        <v>274</v>
+      </c>
+      <c r="O17" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="P17" s="3">
+        <v>274</v>
+      </c>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
@@ -15107,6 +15237,18 @@
       <c r="C18" s="3"/>
       <c r="D18" s="3"/>
       <c r="E18" s="3"/>
+      <c r="H18" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I18" s="3">
+        <v>276</v>
+      </c>
+      <c r="O18" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="P18" s="3">
+        <v>276</v>
+      </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
@@ -15118,6 +15260,18 @@
       <c r="C19" s="3"/>
       <c r="D19" s="3"/>
       <c r="E19" s="3"/>
+      <c r="H19" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="I19" s="3">
+        <v>1634</v>
+      </c>
+      <c r="O19" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="P19" s="3">
+        <v>1634</v>
+      </c>
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
